--- a/ig/document/StructureDefinition-medcom-document-patient.xlsx
+++ b/ig/document/StructureDefinition-medcom-document-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T10:37:57+00:00</t>
+    <t>2026-03-10T10:54:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2740,7 +2740,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -3206,7 +3206,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>141</v>
       </c>
@@ -3670,7 +3670,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>149</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>181</v>
       </c>
@@ -4844,7 +4844,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>212</v>
       </c>
@@ -4963,7 +4963,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>223</v>
       </c>
@@ -5312,7 +5312,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>251</v>
       </c>
@@ -5901,7 +5901,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>260</v>
       </c>
@@ -6020,7 +6020,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>262</v>
       </c>
@@ -6369,7 +6369,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>266</v>
       </c>
@@ -6958,7 +6958,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>274</v>
       </c>
@@ -7075,7 +7075,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>276</v>
       </c>
@@ -7662,7 +7662,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>299</v>
       </c>
@@ -8015,7 +8015,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>305</v>
       </c>
@@ -8253,7 +8253,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>325</v>
       </c>
@@ -8370,7 +8370,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>334</v>
       </c>
@@ -8953,7 +8953,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>374</v>
       </c>
@@ -9072,7 +9072,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
         <v>384</v>
       </c>
@@ -15283,12 +15283,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO109">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/ig/document/StructureDefinition-medcom-document-patient.xlsx
+++ b/ig/document/StructureDefinition-medcom-document-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T10:54:08+00:00</t>
+    <t>2026-04-29T08:07:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
